--- a/llm_prioritized_vulnerabilities.xlsx
+++ b/llm_prioritized_vulnerabilities.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soudas\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6499D2-E8C5-4477-96D8-BFB0621CE738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4525383-857C-435A-93AA-D4B14ECF1192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="103">
   <si>
     <t>image</t>
   </si>
   <si>
-    <t>cve</t>
+    <t>CVE_ID</t>
   </si>
   <si>
     <t>package</t>
@@ -43,6 +43,9 @@
     <t>CVSS_RISK_SCORE</t>
   </si>
   <si>
+    <t>CWE_ID</t>
+  </si>
+  <si>
     <t>url</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>Critical</t>
   </si>
   <si>
+    <t>CWE-187</t>
+  </si>
+  <si>
     <t>https://github.com/advisories/GHSA-v23v-6jw2-98fq</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>expat-2.4.1-r0</t>
   </si>
   <si>
+    <t>CWE-190</t>
+  </si>
+  <si>
     <t>https://security.alpinelinux.org/vuln/CVE-2022-22823</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>golang.org/x/crypto-v0.24.0</t>
   </si>
   <si>
+    <t>CWE-285</t>
+  </si>
+  <si>
     <t>https://github.com/advisories/GHSA-v778-237x-gjrc</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>stdlib-go1.20.3</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>https://nvd.nist.gov/vuln/detail/CVE-2025-22871</t>
   </si>
   <si>
@@ -139,12 +154,12 @@
     <t>Medium</t>
   </si>
   <si>
+    <t>CWE-908</t>
+  </si>
+  <si>
     <t>https://access.redhat.com/security/cve/CVE-2026-0915</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:N/A:N</t>
   </si>
   <si>
@@ -160,6 +175,9 @@
     <t>Negligible</t>
   </si>
   <si>
+    <t>CWE-770</t>
+  </si>
+  <si>
     <t>https://ubuntu.com/security/CVE-2016-20013</t>
   </si>
   <si>
@@ -187,6 +205,9 @@
     <t>util-linux-2.37.4-21.el9</t>
   </si>
   <si>
+    <t>CWE-125</t>
+  </si>
+  <si>
     <t>https://access.redhat.com/security/cve/CVE-2025-14104</t>
   </si>
   <si>
@@ -205,6 +226,9 @@
     <t>krb5-locales-1.17-6ubuntu4.3</t>
   </si>
   <si>
+    <t>CWE-401</t>
+  </si>
+  <si>
     <t>https://ubuntu.com/security/CVE-2024-26458</t>
   </si>
   <si>
@@ -223,6 +247,9 @@
     <t>openssl-1.1.1w-0+deb11u1</t>
   </si>
   <si>
+    <t>CWE-385</t>
+  </si>
+  <si>
     <t>https://security-tracker.debian.org/tracker/CVE-2025-27587</t>
   </si>
   <si>
@@ -245,6 +272,9 @@
   </si>
   <si>
     <t>libc6-2.31-13+deb11u8</t>
+  </si>
+  <si>
+    <t>CWE-200</t>
   </si>
   <si>
     <t>https://security-tracker.debian.org/tracker/CVE-2019-1010024</t>
@@ -661,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.6328125" bestFit="1" customWidth="1"/>
@@ -671,13 +701,14 @@
     <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="170.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="53.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="59.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="170.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,48 +742,54 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2">
-        <v>3.2280000000000003E-2</v>
+        <v>3.4819999999999997E-2</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>80.012912</v>
+        <v>80.013927999999993</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>9.8000000000000007</v>
@@ -761,30 +798,33 @@
         <v>4.3099999999999996E-3</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>78.801724000000007</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>9.1</v>
@@ -793,30 +833,33 @@
         <v>0.33310000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>74.733239999999995</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>9.1</v>
@@ -825,30 +868,33 @@
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>74.600675999999993</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>9.1</v>
@@ -857,62 +903,68 @@
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>74.600675999999993</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
         <v>33</v>
       </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>7.5</v>
       </c>
       <c r="E7">
-        <v>4.0999999999999999E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>50.000163999999998</v>
+        <v>50.000079999999997</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>7.5</v>
@@ -921,286 +973,313 @@
         <v>3.0699999999999998E-3</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>45.001227999999998</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="J8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D9">
         <v>7.5</v>
       </c>
       <c r="E9">
-        <v>4.8999999999999998E-4</v>
+        <v>6.6E-4</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>45.000196000000003</v>
+        <v>45.000264000000001</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="J9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>7.5</v>
       </c>
       <c r="E10">
-        <v>4.8999999999999998E-4</v>
+        <v>6.6E-4</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>45.000196000000003</v>
+        <v>45.000264000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="I10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="J10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D11">
         <v>6.1</v>
       </c>
       <c r="E11">
-        <v>1.4999999999999999E-4</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G11">
-        <v>41.600059999999992</v>
+        <v>41.600023999999998</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="J11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D12">
         <v>6.1</v>
       </c>
       <c r="E12">
-        <v>1.4999999999999999E-4</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G12">
-        <v>41.600059999999992</v>
+        <v>41.600023999999998</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="J12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D13">
         <v>6.1</v>
       </c>
       <c r="E13">
-        <v>1.4999999999999999E-4</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G13">
-        <v>41.600059999999992</v>
+        <v>41.600023999999998</v>
       </c>
       <c r="H13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="K13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D14">
         <v>5.3</v>
       </c>
       <c r="E14">
-        <v>2.0600000000000002E-3</v>
+        <v>2.5699999999999998E-3</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>31.800823999999999</v>
+        <v>31.801027999999999</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="K14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D15">
         <v>5.3</v>
       </c>
       <c r="E15">
-        <v>4.6000000000000001E-4</v>
+        <v>7.1000000000000002E-4</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>31.800184000000002</v>
+        <v>31.800284000000001</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="J15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D16">
         <v>4.0999999999999996</v>
       </c>
       <c r="E16">
-        <v>1.23E-3</v>
+        <v>7.5000000000000002E-4</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G16">
-        <v>24.600491999999999</v>
+        <v>24.600300000000001</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1209,27 +1288,30 @@
         <v>6.4599999999999996E-3</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G17">
         <v>2.5839999999999999E-3</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="J17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1238,30 +1320,33 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>40</v>
-      </c>
-      <c r="K18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="J18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1270,30 +1355,33 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1302,30 +1390,33 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="J20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1334,30 +1425,33 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="J21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1366,30 +1460,33 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1398,19 +1495,22 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" t="s">
-        <v>88</v>
+        <v>97</v>
+      </c>
+      <c r="J23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
